--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241025120000</t>
+    <t>20241209120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T12:00:00+01:00</t>
+    <t>2024-12-09T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -145,6 +145,24 @@
   </si>
   <si>
     <t>Professionnel de Santé Libéral (PSL)</t>
+  </si>
+  <si>
+    <t>ADMIN_METIER</t>
+  </si>
+  <si>
+    <t>Administrateur Métier</t>
+  </si>
+  <si>
+    <t>SUPPORT</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>REF_MSP</t>
+  </si>
+  <si>
+    <t>Référent Maison de Santé Pluriprofessionnelle</t>
   </si>
   <si>
     <t/>
@@ -423,7 +441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -499,15 +517,39 @@
         <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
